--- a/output/trend_summary.xlsx
+++ b/output/trend_summary.xlsx
@@ -290,12 +290,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$13:$A$48</f>
+              <f>'Dashboard'!$A$13:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$B$13:$B$48</f>
+              <f>'Dashboard'!$B$13:$B$49</f>
             </numRef>
           </val>
         </ser>
@@ -331,12 +331,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$13:$A$48</f>
+              <f>'Dashboard'!$A$13:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$K$13:$K$48</f>
+              <f>'Dashboard'!$K$13:$K$49</f>
             </numRef>
           </val>
         </ser>
@@ -480,12 +480,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$13:$A$48</f>
+              <f>'Dashboard'!$A$13:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$D$13:$D$48</f>
+              <f>'Dashboard'!$D$13:$D$49</f>
             </numRef>
           </val>
         </ser>
@@ -603,12 +603,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$13:$A$48</f>
+              <f>'Dashboard'!$A$13:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$E$13:$E$48</f>
+              <f>'Dashboard'!$E$13:$E$49</f>
             </numRef>
           </val>
         </ser>
@@ -725,12 +725,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$13:$A$48</f>
+              <f>'Dashboard'!$A$13:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$F$13:$F$48</f>
+              <f>'Dashboard'!$F$13:$F$49</f>
             </numRef>
           </val>
         </ser>
@@ -847,12 +847,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$13:$A$48</f>
+              <f>'Dashboard'!$A$13:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$J$13:$J$48</f>
+              <f>'Dashboard'!$J$13:$J$49</f>
             </numRef>
           </val>
         </ser>
@@ -961,12 +961,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$13:$A$48</f>
+              <f>'Dashboard'!$A$13:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$M$13:$M$48</f>
+              <f>'Dashboard'!$M$13:$M$49</f>
             </numRef>
           </val>
         </ser>
@@ -999,12 +999,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$13:$A$48</f>
+              <f>'Dashboard'!$A$13:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$L$13:$L$48</f>
+              <f>'Dashboard'!$L$13:$L$49</f>
             </numRef>
           </val>
         </ser>
@@ -1136,7 +1136,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!B92</f>
+              <f>'Dashboard'!B94</f>
             </strRef>
           </tx>
           <spPr>
@@ -1146,12 +1146,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$93:$A$131</f>
+              <f>'Dashboard'!$A$95:$A$134</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$B$93:$B$131</f>
+              <f>'Dashboard'!$B$95:$B$134</f>
             </numRef>
           </val>
         </ser>
@@ -1160,7 +1160,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!C92</f>
+              <f>'Dashboard'!C94</f>
             </strRef>
           </tx>
           <spPr>
@@ -1170,12 +1170,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$93:$A$131</f>
+              <f>'Dashboard'!$A$95:$A$134</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$C$93:$C$131</f>
+              <f>'Dashboard'!$C$95:$C$134</f>
             </numRef>
           </val>
         </ser>
@@ -1184,7 +1184,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!D92</f>
+              <f>'Dashboard'!D94</f>
             </strRef>
           </tx>
           <spPr>
@@ -1194,12 +1194,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$93:$A$131</f>
+              <f>'Dashboard'!$A$95:$A$134</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$D$93:$D$131</f>
+              <f>'Dashboard'!$D$95:$D$134</f>
             </numRef>
           </val>
         </ser>
@@ -1208,7 +1208,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!E92</f>
+              <f>'Dashboard'!E94</f>
             </strRef>
           </tx>
           <spPr>
@@ -1218,12 +1218,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$93:$A$131</f>
+              <f>'Dashboard'!$A$95:$A$134</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$E$93:$E$131</f>
+              <f>'Dashboard'!$E$95:$E$134</f>
             </numRef>
           </val>
         </ser>
@@ -1232,7 +1232,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!F92</f>
+              <f>'Dashboard'!F94</f>
             </strRef>
           </tx>
           <spPr>
@@ -1242,12 +1242,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$93:$A$131</f>
+              <f>'Dashboard'!$A$95:$A$134</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$F$93:$F$131</f>
+              <f>'Dashboard'!$F$95:$F$134</f>
             </numRef>
           </val>
         </ser>
@@ -1347,7 +1347,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!B52</f>
+              <f>'Dashboard'!B53</f>
             </strRef>
           </tx>
           <spPr>
@@ -1357,12 +1357,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$53:$A$88</f>
+              <f>'Dashboard'!$A$54:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$B$53:$B$88</f>
+              <f>'Dashboard'!$B$54:$B$90</f>
             </numRef>
           </val>
         </ser>
@@ -1371,7 +1371,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!C52</f>
+              <f>'Dashboard'!C53</f>
             </strRef>
           </tx>
           <spPr>
@@ -1381,12 +1381,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$53:$A$88</f>
+              <f>'Dashboard'!$A$54:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$C$53:$C$88</f>
+              <f>'Dashboard'!$C$54:$C$90</f>
             </numRef>
           </val>
         </ser>
@@ -1395,7 +1395,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!D52</f>
+              <f>'Dashboard'!D53</f>
             </strRef>
           </tx>
           <spPr>
@@ -1405,12 +1405,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$53:$A$88</f>
+              <f>'Dashboard'!$A$54:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$D$53:$D$88</f>
+              <f>'Dashboard'!$D$54:$D$90</f>
             </numRef>
           </val>
         </ser>
@@ -1419,7 +1419,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!E52</f>
+              <f>'Dashboard'!E53</f>
             </strRef>
           </tx>
           <spPr>
@@ -1429,12 +1429,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$53:$A$88</f>
+              <f>'Dashboard'!$A$54:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$E$53:$E$88</f>
+              <f>'Dashboard'!$E$54:$E$90</f>
             </numRef>
           </val>
         </ser>
@@ -1443,7 +1443,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!F52</f>
+              <f>'Dashboard'!F53</f>
             </strRef>
           </tx>
           <spPr>
@@ -1453,12 +1453,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$53:$A$88</f>
+              <f>'Dashboard'!$A$54:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$F$53:$F$88</f>
+              <f>'Dashboard'!$F$54:$F$90</f>
             </numRef>
           </val>
         </ser>
@@ -1467,7 +1467,7 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!G52</f>
+              <f>'Dashboard'!G53</f>
             </strRef>
           </tx>
           <spPr>
@@ -1477,12 +1477,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$53:$A$88</f>
+              <f>'Dashboard'!$A$54:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$G$53:$G$88</f>
+              <f>'Dashboard'!$G$54:$G$90</f>
             </numRef>
           </val>
         </ser>
@@ -1491,7 +1491,7 @@
           <order val="6"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!H52</f>
+              <f>'Dashboard'!H53</f>
             </strRef>
           </tx>
           <spPr>
@@ -1501,12 +1501,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$53:$A$88</f>
+              <f>'Dashboard'!$A$54:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$H$53:$H$88</f>
+              <f>'Dashboard'!$H$54:$H$90</f>
             </numRef>
           </val>
         </ser>
@@ -1515,7 +1515,7 @@
           <order val="7"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!I52</f>
+              <f>'Dashboard'!I53</f>
             </strRef>
           </tx>
           <spPr>
@@ -1525,12 +1525,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$53:$A$88</f>
+              <f>'Dashboard'!$A$54:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$I$53:$I$88</f>
+              <f>'Dashboard'!$I$54:$I$90</f>
             </numRef>
           </val>
         </ser>
@@ -1539,7 +1539,7 @@
           <order val="8"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!J52</f>
+              <f>'Dashboard'!J53</f>
             </strRef>
           </tx>
           <spPr>
@@ -1549,12 +1549,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$53:$A$88</f>
+              <f>'Dashboard'!$A$54:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$J$53:$J$88</f>
+              <f>'Dashboard'!$J$54:$J$90</f>
             </numRef>
           </val>
         </ser>
@@ -1563,7 +1563,7 @@
           <order val="9"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!K52</f>
+              <f>'Dashboard'!K53</f>
             </strRef>
           </tx>
           <spPr>
@@ -1573,12 +1573,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$53:$A$88</f>
+              <f>'Dashboard'!$A$54:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$K$53:$K$88</f>
+              <f>'Dashboard'!$K$54:$K$90</f>
             </numRef>
           </val>
         </ser>
@@ -2125,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M131"/>
+  <dimension ref="A1:M134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2202,25 +2202,25 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="5" t="n">
-        <v>1038.76</v>
+        <v>1071.95</v>
       </c>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>84:52:06</t>
+          <t>87:28:00</t>
         </is>
       </c>
       <c r="F6" s="6" t="n"/>
       <c r="G6" s="5" t="n">
-        <v>153.5</v>
+        <v>153.3</v>
       </c>
       <c r="H6" s="6" t="n"/>
       <c r="I6" s="5" t="n">
-        <v>22.15</v>
+        <v>22.2</v>
       </c>
       <c r="J6" s="6" t="n"/>
     </row>
@@ -2259,24 +2259,24 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="5" t="n">
-        <v>18.01</v>
+        <v>10.44</v>
       </c>
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>01:28:35</t>
+          <t>00:46:06</t>
         </is>
       </c>
       <c r="F9" s="6" t="n"/>
       <c r="G9" s="5" t="n"/>
       <c r="H9" s="6" t="n"/>
       <c r="I9" s="5" t="n">
-        <v>23.78</v>
+        <v>24.51</v>
       </c>
       <c r="J9" s="6" t="n"/>
     </row>
@@ -3700,7 +3700,7 @@
         <v>23.56</v>
       </c>
       <c r="F47" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G47" t="n">
         <v>2</v>
@@ -3712,7 +3712,7 @@
         <v>15.01</v>
       </c>
       <c r="J47" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K47" t="n">
         <v>3.49</v>
@@ -3721,7 +3721,7 @@
         <v>22.57460683151558</v>
       </c>
       <c r="M47" t="n">
-        <v>9.43125</v>
+        <v>9.780555555555555</v>
       </c>
     </row>
     <row r="48">
@@ -3731,146 +3731,154 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>18.01</v>
+        <v>40.76</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>01:28:35</t>
+          <t>03:18:23</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>23.78</v>
+        <v>23.66</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>8</v>
+        <v>14.01</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>16.74</v>
+      </c>
+      <c r="J48" t="n">
+        <v>9.9</v>
       </c>
       <c r="K48" t="n">
-        <v>1.48</v>
+        <v>3.31</v>
       </c>
       <c r="L48" t="n">
-        <v>22.57460683151558</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
+        <v>23.17031951314489</v>
+      </c>
+      <c r="M48" t="n">
+        <v>9.919166666666666</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>00:46:06</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>24.51</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L49" t="n">
+        <v>23.17031951314489</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>Week Start</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>Brick Run</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>Easy Run</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>Interval Run</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>Long Run</t>
         </is>
       </c>
-      <c r="F52" s="7" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>Park Run</t>
         </is>
       </c>
-      <c r="G52" s="7" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>Race Day</t>
         </is>
       </c>
-      <c r="H52" s="7" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>Recovery Run</t>
         </is>
       </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t>Tempo Run</t>
         </is>
       </c>
-      <c r="J52" s="7" t="inlineStr">
+      <c r="J53" s="7" t="inlineStr">
         <is>
           <t>Threshold 1</t>
         </is>
       </c>
-      <c r="K52" s="7" t="inlineStr">
+      <c r="K53" s="7" t="inlineStr">
         <is>
           <t>Threshold 2</t>
         </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" t="n">
-        <v>7.07</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>9.949999999999999</v>
+        <v>7.07</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>20.01</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -3885,7 +3893,7 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>10.03</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -3894,23 +3902,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>6.31</v>
+        <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>26.01</v>
+        <v>20.01</v>
       </c>
       <c r="F55" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -3919,7 +3927,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>17.11</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -3931,32 +3939,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>6.31</v>
       </c>
       <c r="C56" t="n">
-        <v>17.2</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>26.01</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="G56" t="n">
-        <v>21.16</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>17.11</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3968,14 +3976,14 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>7.51</v>
+        <v>17.2</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -3987,13 +3995,13 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>21.16</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>18.03</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4005,20 +4013,20 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>8.42</v>
+        <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>16.28</v>
+        <v>7.51</v>
       </c>
       <c r="D58" t="n">
-        <v>16.65</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>24.34</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -4030,7 +4038,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>18.03</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4042,20 +4050,20 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>8.42</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>16.28</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>16.65</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>24.34</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -4067,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>17.1</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4079,20 +4087,20 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>12.22</v>
+        <v>0</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>24.47</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -4104,10 +4112,10 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>17.1</v>
       </c>
       <c r="J60" t="n">
-        <v>17.26</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -4116,20 +4124,20 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>12.22</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>31.21</v>
+        <v>24.47</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -4141,10 +4149,10 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>11.04</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>20.12</v>
+        <v>17.26</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -4153,7 +4161,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -4166,7 +4174,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>18.49</v>
+        <v>31.21</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -4178,10 +4186,10 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>15.37</v>
+        <v>11.04</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>20.12</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -4190,20 +4198,20 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>17.01</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>22.33</v>
+        <v>18.49</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -4215,7 +4223,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>15.37</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -4227,20 +4235,20 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>17.01</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>22.33</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -4252,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>20.86</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>10.01</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -4264,7 +4272,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -4277,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>20.58</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -4289,10 +4297,10 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>20.86</v>
       </c>
       <c r="J65" t="n">
-        <v>13.51</v>
+        <v>10.01</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -4301,11 +4309,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>16.73</v>
+        <v>0</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
@@ -4314,7 +4322,7 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>20.58</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -4329,7 +4337,7 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>16.24</v>
+        <v>13.51</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -4338,11 +4346,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0</v>
+        <v>16.73</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -4354,7 +4362,7 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -4366,7 +4374,7 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>29.41</v>
+        <v>16.24</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -4375,14 +4383,14 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>10.01</v>
+        <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -4391,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -4403,23 +4411,23 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>16.18</v>
+        <v>29.41</v>
       </c>
       <c r="K68" t="n">
-        <v>5.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>10.01</v>
       </c>
       <c r="C69" t="n">
-        <v>15.33</v>
+        <v>4.32</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -4431,7 +4439,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>26.45</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -4440,23 +4448,23 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>16.18</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>19.95</v>
+        <v>15.33</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -4468,7 +4476,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>20.1</v>
+        <v>26.45</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -4486,14 +4494,14 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>30.71</v>
+        <v>19.95</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -4505,7 +4513,7 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>20.1</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -4523,14 +4531,14 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>11.33</v>
+        <v>30.71</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -4560,14 +4568,14 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>9.07</v>
+        <v>11.33</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -4579,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>41.91</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -4597,14 +4605,14 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>5.6</v>
+        <v>9.07</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
@@ -4613,10 +4621,10 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>41.91</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -4634,14 +4642,14 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>10.01</v>
+        <v>5.6</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -4671,14 +4679,14 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>10.83</v>
+        <v>10.01</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -4687,7 +4695,7 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>5.04</v>
+        <v>5.05</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -4708,14 +4716,14 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>21.02</v>
+        <v>10.83</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
@@ -4724,7 +4732,7 @@
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>5.03</v>
+        <v>5.04</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -4745,14 +4753,14 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>10.14</v>
+        <v>21.02</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -4761,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -4782,14 +4790,14 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>9.74</v>
+        <v>10.14</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
@@ -4819,14 +4827,14 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>13.73</v>
+        <v>9.74</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -4856,14 +4864,14 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>5.45</v>
+        <v>13.73</v>
       </c>
       <c r="D81" t="n">
         <v>0</v>
@@ -4893,14 +4901,14 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>29.91</v>
+        <v>5.45</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -4930,14 +4938,14 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>7.44</v>
+        <v>29.91</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
@@ -4967,14 +4975,14 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>9.08</v>
+        <v>7.44</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
@@ -5004,14 +5012,14 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>9.08</v>
       </c>
       <c r="D85" t="n">
         <v>0</v>
@@ -5020,7 +5028,7 @@
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -5041,14 +5049,14 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>19.02</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -5057,19 +5065,19 @@
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>5.03</v>
+        <v>5.06</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>8.01</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -5078,35 +5086,35 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>7.02</v>
+        <v>19.02</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>15.01</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>5.06</v>
+        <v>5.03</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>5.01</v>
+        <v>5.26</v>
       </c>
       <c r="I87" t="n">
-        <v>12.16</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>8.01</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -5115,124 +5123,154 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="F88" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="I88" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B88" t="n">
-        <v>0</v>
-      </c>
-      <c r="C88" t="n">
-        <v>8</v>
-      </c>
-      <c r="D88" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="n">
+      <c r="B89" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
         <v>10.01</v>
       </c>
-      <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Week Start</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Run</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Bike</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Swim</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Strength</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="C93" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" t="n">
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="C94" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" t="n">
-        <v>0</v>
+          <t>Week Start</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Bike</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Swim</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Strength</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>4.25</v>
+        <v>1.32</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -5250,11 +5288,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>2.97</v>
+        <v>2.58</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -5272,11 +5310,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>2</v>
+        <v>4.25</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -5294,11 +5332,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>5.28</v>
+        <v>2.97</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -5316,11 +5354,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -5338,11 +5376,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>4.27</v>
+        <v>5.28</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
@@ -5360,11 +5398,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>4.9</v>
+        <v>1.34</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -5382,11 +5420,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>2.71</v>
+        <v>4.27</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -5404,11 +5442,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>3.19</v>
+        <v>4.9</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
@@ -5426,11 +5464,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>2.28</v>
+        <v>2.71</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -5448,11 +5486,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>2.93</v>
+        <v>3.19</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -5470,11 +5508,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
@@ -5492,11 +5530,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>2.53</v>
+        <v>2.93</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -5514,11 +5552,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -5536,17 +5574,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
@@ -5558,17 +5596,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="E110" t="n">
         <v>0</v>
@@ -5580,7 +5618,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -5590,7 +5628,7 @@
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>1.66</v>
+        <v>0.86</v>
       </c>
       <c r="E111" t="n">
         <v>0</v>
@@ -5602,17 +5640,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>3.46</v>
+        <v>3.65</v>
       </c>
       <c r="C112" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>3.45</v>
+        <v>1.23</v>
       </c>
       <c r="E112" t="n">
         <v>0</v>
@@ -5624,17 +5662,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>0.9</v>
+        <v>1.66</v>
       </c>
       <c r="E113" t="n">
         <v>0</v>
@@ -5646,17 +5684,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.92</v>
+        <v>3.46</v>
       </c>
       <c r="C114" t="n">
-        <v>4.7</v>
+        <v>4.49</v>
       </c>
       <c r="D114" t="n">
-        <v>0.93</v>
+        <v>3.45</v>
       </c>
       <c r="E114" t="n">
         <v>0</v>
@@ -5668,17 +5706,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>5.53</v>
+        <v>2.72</v>
       </c>
       <c r="C115" t="n">
-        <v>6.3</v>
+        <v>7.01</v>
       </c>
       <c r="D115" t="n">
-        <v>5.88</v>
+        <v>0.9</v>
       </c>
       <c r="E115" t="n">
         <v>0</v>
@@ -5690,17 +5728,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="C116" t="n">
-        <v>2.28</v>
+        <v>4.7</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="E116" t="n">
         <v>0</v>
@@ -5712,17 +5750,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.83</v>
+        <v>5.53</v>
       </c>
       <c r="C117" t="n">
-        <v>1.55</v>
+        <v>7.41</v>
       </c>
       <c r="D117" t="n">
-        <v>0.86</v>
+        <v>1.07</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
@@ -5734,17 +5772,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>5.2</v>
+        <v>2.28</v>
       </c>
       <c r="D118" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -5756,17 +5794,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1.25</v>
+        <v>0.83</v>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="D119" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
@@ -5778,17 +5816,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>2.07</v>
+        <v>1.16</v>
       </c>
       <c r="C120" t="n">
-        <v>1.61</v>
+        <v>5.2</v>
       </c>
       <c r="D120" t="n">
-        <v>1.2</v>
+        <v>0.46</v>
       </c>
       <c r="E120" t="n">
         <v>0</v>
@@ -5800,17 +5838,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.83</v>
+        <v>1.25</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="E121" t="n">
         <v>0</v>
@@ -5822,17 +5860,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.82</v>
+        <v>2.07</v>
       </c>
       <c r="C122" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="D122" t="n">
-        <v>0.41</v>
+        <v>1.2</v>
       </c>
       <c r="E122" t="n">
         <v>0</v>
@@ -5844,17 +5882,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
@@ -5866,17 +5904,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.44</v>
+        <v>0.82</v>
       </c>
       <c r="C124" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>0.54</v>
+        <v>0.41</v>
       </c>
       <c r="E124" t="n">
         <v>0</v>
@@ -5888,17 +5926,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>2.57</v>
+        <v>1.08</v>
       </c>
       <c r="C125" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E125" t="n">
         <v>0</v>
@@ -5910,17 +5948,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.59</v>
+        <v>0.44</v>
       </c>
       <c r="C126" t="n">
-        <v>4.5</v>
+        <v>1.51</v>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="E126" t="n">
         <v>0</v>
@@ -5932,17 +5970,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.68</v>
+        <v>2.57</v>
       </c>
       <c r="C127" t="n">
-        <v>16.75</v>
+        <v>3.12</v>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E127" t="n">
         <v>0</v>
@@ -5954,14 +5992,14 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.31</v>
+        <v>0.59</v>
       </c>
       <c r="C128" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -5976,20 +6014,20 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>3.11</v>
+        <v>0.68</v>
       </c>
       <c r="C129" t="n">
-        <v>0.92</v>
+        <v>16.75</v>
       </c>
       <c r="D129" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="E129" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="F129" t="n">
         <v>0</v>
@@ -5998,20 +6036,20 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>3.49</v>
+        <v>0.31</v>
       </c>
       <c r="C130" t="n">
-        <v>2.17</v>
+        <v>1.5</v>
       </c>
       <c r="D130" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="E130" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="F130" t="n">
         <v>0</v>
@@ -6020,22 +6058,88 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E131" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="C132" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B131" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="C131" t="n">
-        <v>0</v>
-      </c>
-      <c r="D131" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E131" t="n">
+      <c r="B133" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E133" t="n">
         <v>0.55</v>
       </c>
-      <c r="F131" t="n">
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6520,7 +6624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6813,7 +6917,7 @@
         <v>162</v>
       </c>
       <c r="G7" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -6856,8 +6960,11 @@
       <c r="F8" t="n">
         <v>154</v>
       </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>45</v>
@@ -6870,6 +6977,47 @@
       </c>
       <c r="L8" t="n">
         <v>23.41</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00:46:06</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>04:24</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>154</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>30</v>
+      </c>
+      <c r="J9" t="n">
+        <v>24.51</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L9" t="n">
+        <v>23.56</v>
       </c>
     </row>
   </sheetData>
@@ -6883,7 +7031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7274,7 +7422,7 @@
         <v>184</v>
       </c>
       <c r="J7" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
@@ -7328,8 +7476,11 @@
       <c r="I8" t="n">
         <v>170</v>
       </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>14</v>
@@ -7342,6 +7493,58 @@
       </c>
       <c r="O8" t="n">
         <v>24.51</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>tempo_run</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>00:17:57</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>03:45</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>168.2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>176</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>13</v>
+      </c>
+      <c r="M9" t="n">
+        <v>26.39</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O9" t="n">
+        <v>24.8</v>
       </c>
     </row>
   </sheetData>
@@ -7355,7 +7558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8359,21 +8562,21 @@
         <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>79.51000000000001</v>
+        <v>214.64</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>06:18:03</t>
+          <t>07:24:24</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>135.5</v>
+        <v>136.5</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>3847</v>
+        <v>3464</v>
       </c>
     </row>
     <row r="32">
@@ -8420,24 +8623,24 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>44.77</v>
+        <v>2.86</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>05:52:44</t>
+          <t>01:04:15</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>123.5</v>
+        <v>117</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>3502</v>
+        <v>595</v>
       </c>
     </row>
     <row r="34">
@@ -9590,7 +9793,7 @@
         <v>149.4</v>
       </c>
       <c r="G68" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="H68" t="n">
         <v>5</v>
@@ -9671,28 +9874,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Run</t>
+          <t>Bike</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>18.01</v>
+        <v>18.89</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>01:28:35</t>
+          <t>01:00:01</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>142.5</v>
+        <v>133</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>1119</v>
+        <v>472</v>
       </c>
     </row>
     <row r="72">
@@ -9703,28 +9906,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Strength</t>
+          <t>Run</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>40.76</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>00:32:49</t>
+          <t>03:18:23</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>83</v>
+        <v>144.8</v>
+      </c>
+      <c r="G72" t="n">
+        <v>3</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I72" t="n">
-        <v>126</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="73">
@@ -9735,28 +9941,124 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t>Strength</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>00:32:49</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>83</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
           <t>Swim</t>
         </is>
       </c>
-      <c r="C73" t="n">
-        <v>1</v>
-      </c>
-      <c r="D73" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>00:24:45</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>117</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>227</v>
+      <c r="C74" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>00:51:08</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Bike</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>00:30:09</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>116</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>00:46:06</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>154</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>678</v>
       </c>
     </row>
   </sheetData>
@@ -9796,7 +10098,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3">
@@ -9806,7 +10108,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1038.76</v>
+        <v>1071.95</v>
       </c>
     </row>
     <row r="4">
@@ -9817,7 +10119,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>84:52:06</t>
+          <t>87:28:00</t>
         </is>
       </c>
     </row>
@@ -9828,7 +10130,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>153.5</v>
+        <v>153.3</v>
       </c>
     </row>
     <row r="6">
@@ -9838,7 +10140,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7079</v>
+        <v>7281</v>
       </c>
     </row>
   </sheetData>
@@ -9914,14 +10216,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C2" t="n">
-        <v>344.94</v>
+        <v>350.95</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>29:07:32</t>
+          <t>29:38:03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9930,13 +10232,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>149.3</v>
+        <v>149.1</v>
       </c>
       <c r="G2" t="n">
-        <v>2928</v>
+        <v>2958</v>
       </c>
       <c r="H2" t="n">
-        <v>22.04</v>
+        <v>22.07</v>
       </c>
     </row>
     <row r="3">
@@ -9978,29 +10280,29 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>202.45</v>
+        <v>219.19</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16:46:47</t>
+          <t>18:06:04</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>04:58</t>
+          <t>04:57</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>146.7</v>
+        <v>147.3</v>
       </c>
       <c r="G4" t="n">
-        <v>1351</v>
+        <v>1493</v>
       </c>
       <c r="H4" t="n">
-        <v>22.85</v>
+        <v>22.84</v>
       </c>
     </row>
     <row r="5">
@@ -10010,29 +10312,29 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>121.68</v>
+        <v>132.12</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>09:24:12</t>
+          <t>10:10:18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>04:38</t>
+          <t>04:37</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>153</v>
+        <v>153.1</v>
       </c>
       <c r="G5" t="n">
-        <v>811</v>
+        <v>841</v>
       </c>
       <c r="H5" t="n">
-        <v>23.49</v>
+        <v>23.56</v>
       </c>
     </row>
     <row r="6">
@@ -10300,14 +10602,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C2" t="n">
-        <v>946.86</v>
+        <v>980.05</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>77:17:58</t>
+          <t>79:53:52</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10316,13 +10618,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>154.2</v>
+        <v>154.1</v>
       </c>
       <c r="G2" t="n">
-        <v>7079</v>
+        <v>7281</v>
       </c>
       <c r="H2" t="n">
-        <v>22.06</v>
+        <v>22.12</v>
       </c>
     </row>
     <row r="3">
@@ -10368,7 +10670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12011,7 +12313,7 @@
         <v>149.4</v>
       </c>
       <c r="G36" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="H36" t="n">
         <v>5</v>
@@ -12039,41 +12341,88 @@
         </is>
       </c>
       <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" t="n">
+        <v>40.76</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>03:18:23</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>04:52</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>144.8</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3</v>
+      </c>
+      <c r="H37" t="n">
         <v>2</v>
       </c>
-      <c r="C37" t="n">
-        <v>18.01</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>01:28:35</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>04:55</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>142.5</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
       <c r="I37" t="n">
-        <v>45</v>
+        <v>217</v>
       </c>
       <c r="J37" t="n">
-        <v>8</v>
+        <v>14.01</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>16.74</v>
       </c>
       <c r="L37" t="n">
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>23.78</v>
+        <v>23.66</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>00:46:06</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>04:24</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>154</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>30</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" t="n">
+        <v>24.51</v>
       </c>
     </row>
   </sheetData>
@@ -12087,7 +12436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15097,7 +15446,7 @@
         <v>162</v>
       </c>
       <c r="H73" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="I73" t="n">
         <v>1</v>
@@ -15121,32 +15470,35 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D74" t="n">
-        <v>8</v>
+        <v>14.01</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>00:42:29</t>
+          <t>01:13:00</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>05:18</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>131</v>
+        <v>136</v>
+      </c>
+      <c r="H74" t="n">
+        <v>2</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K74" t="n">
-        <v>23.96</v>
+        <v>23.52</v>
       </c>
     </row>
     <row r="75">
@@ -15157,36 +15509,119 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
+          <t>Long Run</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>01:19:17</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>04:44</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>153</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>142</v>
+      </c>
+      <c r="K75" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>Tempo Run</t>
         </is>
       </c>
-      <c r="C75" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" t="n">
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="n">
         <v>10.01</v>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>00:46:06</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>04:36</t>
         </is>
       </c>
-      <c r="G75" t="n">
+      <c r="G76" t="n">
         <v>154</v>
       </c>
-      <c r="I75" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" t="n">
+      <c r="H76" t="n">
+        <v>4</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" t="n">
         <v>45</v>
       </c>
-      <c r="K75" t="n">
+      <c r="K76" t="n">
         <v>23.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Tempo Run</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>00:46:06</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>04:24</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>154</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>30</v>
+      </c>
+      <c r="K77" t="n">
+        <v>24.51</v>
       </c>
     </row>
   </sheetData>
@@ -16385,38 +16820,41 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>14.01</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>00:42:29</t>
+          <t>01:13:00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>05:18</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>131</v>
+        <v>136</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J28" t="n">
-        <v>23.96</v>
+        <v>23.52</v>
       </c>
       <c r="K28" t="n">
-        <v>1.23</v>
+        <v>0.79</v>
       </c>
       <c r="L28" t="n">
-        <v>23.34</v>
+        <v>23.23</v>
       </c>
     </row>
   </sheetData>
@@ -17615,24 +18053,38 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>6.01</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>00:00:00</t>
-        </is>
+          <t>00:30:31</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>05:04</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>141</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="J28" t="n">
+        <v>23.28</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.55</v>
       </c>
       <c r="L28" t="n">
-        <v>22.57</v>
+        <v>23.17</v>
       </c>
     </row>
   </sheetData>
@@ -17646,7 +18098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18012,6 +18464,47 @@
         <v>22.8</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>01:19:17</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>04:44</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>153</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>142</v>
+      </c>
+      <c r="J9" t="n">
+        <v>23</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="L9" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/trend_summary.xlsx
+++ b/output/trend_summary.xlsx
@@ -20,16 +20,27 @@
     <sheet name="Outdoor Tempo Efficiency" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Tempo Work Trend" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Weekly by Sport" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Easy HR Drift" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Long HR Drift" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Running Work Segments" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Easy HR Drift'!$A$1:$S$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Long HR Drift'!$A$1:$S$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Running Work Segments'!$A$1:$M$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,6 +67,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="6">
@@ -86,7 +101,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -156,11 +171,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9E1F2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9E1F2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E1F2"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -177,6 +204,17 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="45" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1321,7 +1359,6 @@
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -2169,31 +2206,31 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Total Sessions</t>
         </is>
       </c>
       <c r="B5" s="4" t="n"/>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Total Distance (km)</t>
         </is>
       </c>
       <c r="D5" s="4" t="n"/>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Total Time</t>
         </is>
       </c>
       <c r="F5" s="4" t="n"/>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Average HR</t>
         </is>
       </c>
       <c r="H5" s="4" t="n"/>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>Overall Efficiency</t>
         </is>
@@ -2225,31 +2262,31 @@
       <c r="J6" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Latest Week</t>
         </is>
       </c>
       <c r="B8" s="4" t="n"/>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Latest Week Distance</t>
         </is>
       </c>
       <c r="D8" s="4" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>Latest Week Time</t>
         </is>
       </c>
       <c r="F8" s="4" t="n"/>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>Latest Week Avg RPE</t>
         </is>
       </c>
       <c r="H8" s="4" t="n"/>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>Latest Week Efficiency</t>
         </is>
@@ -2273,7 +2310,9 @@
         </is>
       </c>
       <c r="F9" s="6" t="n"/>
-      <c r="G9" s="5" t="n"/>
+      <c r="G9" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="H9" s="6" t="n"/>
       <c r="I9" s="5" t="n">
         <v>24.51</v>
@@ -3745,7 +3784,7 @@
         <v>23.66</v>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -3757,7 +3796,7 @@
         <v>16.74</v>
       </c>
       <c r="J48" t="n">
-        <v>9.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K48" t="n">
         <v>3.31</v>
@@ -3766,7 +3805,7 @@
         <v>23.17031951314489</v>
       </c>
       <c r="M48" t="n">
-        <v>9.919166666666666</v>
+        <v>8.679270833333334</v>
       </c>
     </row>
     <row r="49">
@@ -3789,6 +3828,9 @@
       <c r="E49" t="n">
         <v>24.51</v>
       </c>
+      <c r="F49" t="n">
+        <v>5</v>
+      </c>
       <c r="G49" t="n">
         <v>1</v>
       </c>
@@ -3797,12 +3839,18 @@
       </c>
       <c r="I49" t="n">
         <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>3.8</v>
       </c>
       <c r="K49" t="n">
         <v>0.77</v>
       </c>
       <c r="L49" t="n">
         <v>23.17031951314489</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3.841666666666667</v>
       </c>
     </row>
     <row r="53">
@@ -7004,8 +7052,11 @@
       <c r="F9" t="n">
         <v>154</v>
       </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>30</v>
@@ -7531,8 +7582,11 @@
       <c r="I9" t="n">
         <v>176</v>
       </c>
+      <c r="J9" t="n">
+        <v>5</v>
+      </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>13</v>
@@ -9924,10 +9978,10 @@
         <v>144.8</v>
       </c>
       <c r="G72" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="H72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I72" t="n">
         <v>2658</v>
@@ -10054,14 +10108,3851 @@
       <c r="F76" t="n">
         <v>154</v>
       </c>
+      <c r="G76" t="n">
+        <v>5</v>
+      </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" t="n">
         <v>678</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Session Name</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Analysis Segment</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Segment Distance (km)</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>First Half Range</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>First Half Pace</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>First Half Avg HR</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>First Half Ascent</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>Second Half Range</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>Second Half Pace</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>Second Half Avg HR</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>Second Half Ascent</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>HR Drift %</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>Pace Change %</t>
+        </is>
+      </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>Aerobic Decoupling %</t>
+        </is>
+      </c>
+      <c r="P1" s="9" t="inlineStr">
+        <is>
+          <t>Ascent Difference</t>
+        </is>
+      </c>
+      <c r="Q1" s="9" t="inlineStr">
+        <is>
+          <t>Analysis Source</t>
+        </is>
+      </c>
+      <c r="R1" s="9" t="inlineStr">
+        <is>
+          <t>Context Flag</t>
+        </is>
+      </c>
+      <c r="S1" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0-7.07 km</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0-3.535 km</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="n">
+        <v>0.003348410733930536</v>
+      </c>
+      <c r="G2" s="11" t="n">
+        <v>155.6390775263155</v>
+      </c>
+      <c r="H2" s="11" t="n">
+        <v>24.605</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3.535-7.07 km</t>
+        </is>
+      </c>
+      <c r="J2" s="12" t="n">
+        <v>0.003321006207763634</v>
+      </c>
+      <c r="K2" s="11" t="n">
+        <v>154.2491730872559</v>
+      </c>
+      <c r="L2" s="11" t="n">
+        <v>14.395</v>
+      </c>
+      <c r="M2" s="13" t="n">
+        <v>-0.008930305043889808</v>
+      </c>
+      <c r="N2" s="13" t="n">
+        <v>-0.008184338285982418</v>
+      </c>
+      <c r="O2" s="13" t="n">
+        <v>-0.01733700419763218</v>
+      </c>
+      <c r="P2" s="11" t="n">
+        <v>-10.21</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0-9.95 km</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0-4.975 km</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="n">
+        <v>0.003656825795644891</v>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>148.0077297452047</v>
+      </c>
+      <c r="H3" s="11" t="n">
+        <v>9.849999999999998</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4.975-9.95 km</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="n">
+        <v>0.00423680904522613</v>
+      </c>
+      <c r="K3" s="11" t="n">
+        <v>150.2073140597974</v>
+      </c>
+      <c r="L3" s="11" t="n">
+        <v>87.14999999999998</v>
+      </c>
+      <c r="M3" s="13" t="n">
+        <v>0.01486128000462728</v>
+      </c>
+      <c r="N3" s="13" t="n">
+        <v>0.158602920125966</v>
+      </c>
+      <c r="O3" s="13" t="n">
+        <v>0.1495305886436502</v>
+      </c>
+      <c r="P3" s="11" t="n">
+        <v>77.29999999999998</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0-9.41 km</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0-4.705 km</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>0.003721649053410477</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>138.3047832136401</v>
+      </c>
+      <c r="H4" s="11" t="n">
+        <v>29.41</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4.705-9.41 km</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="n">
+        <v>0.003704945979454481</v>
+      </c>
+      <c r="K4" s="11" t="n">
+        <v>137.9162707779338</v>
+      </c>
+      <c r="L4" s="11" t="n">
+        <v>34.59</v>
+      </c>
+      <c r="M4" s="13" t="n">
+        <v>-0.002809103392368617</v>
+      </c>
+      <c r="N4" s="13" t="n">
+        <v>-0.004488084103655532</v>
+      </c>
+      <c r="O4" s="13" t="n">
+        <v>-0.007338034503151736</v>
+      </c>
+      <c r="P4" s="11" t="n">
+        <v>5.180000000000003</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0-7.79 km</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0-3.895 km</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>0.003635358722008273</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>141.4237371260422</v>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>28.74</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3.895-7.79 km</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>0.00354383587695526</v>
+      </c>
+      <c r="K5" s="11" t="n">
+        <v>141.19922857622</v>
+      </c>
+      <c r="L5" s="11" t="n">
+        <v>23.26</v>
+      </c>
+      <c r="M5" s="13" t="n">
+        <v>-0.001587488454091956</v>
+      </c>
+      <c r="N5" s="13" t="n">
+        <v>-0.02517573974170362</v>
+      </c>
+      <c r="O5" s="13" t="n">
+        <v>-0.02745700267586426</v>
+      </c>
+      <c r="P5" s="11" t="n">
+        <v>-5.480000000000004</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0-7.51 km</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0-3.755 km</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>0.003224574024757114</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>150.1999273530213</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3.755-7.51 km</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="n">
+        <v>0.003208206958623071</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>151.9425034467188</v>
+      </c>
+      <c r="L6" s="11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M6" s="13" t="n">
+        <v>0.0116017106293389</v>
+      </c>
+      <c r="N6" s="13" t="n">
+        <v>-0.005075729695886322</v>
+      </c>
+      <c r="O6" s="13" t="n">
+        <v>0.006425539221515009</v>
+      </c>
+      <c r="P6" s="11" t="n">
+        <v>-3.02</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0-16.28 km</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0-8.14 km</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>0.003431840931840932</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>144.6993702353331</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>70</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8.14-16.28 km</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>0.003387478387478387</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>144.9251175285426</v>
+      </c>
+      <c r="L7" s="11" t="n">
+        <v>45.00000000000001</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>0.001560112479013442</v>
+      </c>
+      <c r="N7" s="13" t="n">
+        <v>-0.0129267484255885</v>
+      </c>
+      <c r="O7" s="13" t="n">
+        <v>-0.01151795582350701</v>
+      </c>
+      <c r="P7" s="11" t="n">
+        <v>-24.99999999999999</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0-12.22 km</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0-6.11 km</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>0.003416435564041947</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>147.958664855424</v>
+      </c>
+      <c r="H8" s="11" t="n">
+        <v>65.65000000000001</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6.11-12.22 km</t>
+        </is>
+      </c>
+      <c r="J8" s="12" t="n">
+        <v>0.003495806055646481</v>
+      </c>
+      <c r="K8" s="11" t="n">
+        <v>140.8985071391801</v>
+      </c>
+      <c r="L8" s="11" t="n">
+        <v>43.35000000000001</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>-0.04771709533296087</v>
+      </c>
+      <c r="N8" s="13" t="n">
+        <v>0.02323195919159438</v>
+      </c>
+      <c r="O8" s="13" t="n">
+        <v>-0.02626594028985729</v>
+      </c>
+      <c r="P8" s="11" t="n">
+        <v>-22.3</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0-17.01 km</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0-8.505 km</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>0.003404730605090687</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>143.8748773434643</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>54.08000000000001</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8.505-17.01 km</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>0.003116487850284147</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>154.4581010831429</v>
+      </c>
+      <c r="L9" s="11" t="n">
+        <v>61.91999999999999</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>0.07355852484526437</v>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>-0.08465948946902446</v>
+      </c>
+      <c r="O9" s="13" t="n">
+        <v>-0.01763395994995798</v>
+      </c>
+      <c r="P9" s="11" t="n">
+        <v>7.839999999999975</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0-4.32 km</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0-2.16 km</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>0.003417138203017833</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>143.7719375274415</v>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2.16-4.32 km</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="n">
+        <v>0.00351658950617284</v>
+      </c>
+      <c r="K10" s="11" t="n">
+        <v>143.724873529591</v>
+      </c>
+      <c r="L10" s="11" t="n">
+        <v>26.84000000000001</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>-0.0003273517673885173</v>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>0.02910368186664991</v>
+      </c>
+      <c r="O10" s="13" t="n">
+        <v>0.02796241371209129</v>
+      </c>
+      <c r="P10" s="11" t="n">
+        <v>15.68000000000001</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0-6.57 km</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0-3.285 km</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>0.00390902460679858</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>132.2374321187949</v>
+      </c>
+      <c r="H11" s="11" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3.285-6.57 km</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>0.003898630841648346</v>
+      </c>
+      <c r="K11" s="11" t="n">
+        <v>136.3519802986828</v>
+      </c>
+      <c r="L11" s="11" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>0.03111485238303513</v>
+      </c>
+      <c r="N11" s="13" t="n">
+        <v>-0.00265891525270967</v>
+      </c>
+      <c r="O11" s="13" t="n">
+        <v>0.02759037791576757</v>
+      </c>
+      <c r="P11" s="11" t="n">
+        <v>2.859999999999999</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0-8.76 km</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0-4.38 km</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>0.003859927278877051</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>134.8004819541048</v>
+      </c>
+      <c r="H12" s="11" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4.38-8.76 km</t>
+        </is>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>0.003919541687806527</v>
+      </c>
+      <c r="K12" s="11" t="n">
+        <v>132.5624561781997</v>
+      </c>
+      <c r="L12" s="11" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>-0.01660250574376387</v>
+      </c>
+      <c r="N12" s="13" t="n">
+        <v>0.01544443835916498</v>
+      </c>
+      <c r="O12" s="13" t="n">
+        <v>-0.001416487359533702</v>
+      </c>
+      <c r="P12" s="11" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0-8.36 km</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0-4.18 km</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>0.0035275451887294</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>146.5611077096972</v>
+      </c>
+      <c r="H13" s="11" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4.18-8.36 km</t>
+        </is>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>0.003607954545454545</v>
+      </c>
+      <c r="K13" s="11" t="n">
+        <v>149.0192629430093</v>
+      </c>
+      <c r="L13" s="11" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>0.01677222062336758</v>
+      </c>
+      <c r="N13" s="13" t="n">
+        <v>0.0227947063533176</v>
+      </c>
+      <c r="O13" s="13" t="n">
+        <v>0.03841461015491787</v>
+      </c>
+      <c r="P13" s="11" t="n">
+        <v>6.600000000000009</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0-11.59 km</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0-5.795 km</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>0.003596770843319592</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>147.8127117044079</v>
+      </c>
+      <c r="H14" s="11" t="n">
+        <v>57.36</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5.795-11.59 km</t>
+        </is>
+      </c>
+      <c r="J14" s="12" t="n">
+        <v>0.003597330073818426</v>
+      </c>
+      <c r="K14" s="11" t="n">
+        <v>148.6519648666955</v>
+      </c>
+      <c r="L14" s="11" t="n">
+        <v>39.64</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>0.005677814530362868</v>
+      </c>
+      <c r="N14" s="13" t="n">
+        <v>0.0001554812700599317</v>
+      </c>
+      <c r="O14" s="13" t="n">
+        <v>0.005800338384196913</v>
+      </c>
+      <c r="P14" s="11" t="n">
+        <v>-17.72</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0-10.7 km</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0-5.35 km</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>0.003709544825199031</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>146.1270193036683</v>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>41.64999999999999</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5.35-10.7 km</t>
+        </is>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>0.003743293527172032</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>141.0616656071201</v>
+      </c>
+      <c r="L15" s="11" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>-0.03466404584645466</v>
+      </c>
+      <c r="N15" s="13" t="n">
+        <v>0.00909780136467031</v>
+      </c>
+      <c r="O15" s="13" t="n">
+        <v>-0.02656926650797464</v>
+      </c>
+      <c r="P15" s="11" t="n">
+        <v>-2.29999999999999</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0-20.01 km</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0-10.005 km</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>0.003616941529235382</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>146.955478794857</v>
+      </c>
+      <c r="H16" s="11" t="n">
+        <v>126.09</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10.005-20.01 km</t>
+        </is>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>0.003708099653876765</v>
+      </c>
+      <c r="K16" s="11" t="n">
+        <v>143.9168278529981</v>
+      </c>
+      <c r="L16" s="11" t="n">
+        <v>106.9100000000001</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>-0.02067735729744913</v>
+      </c>
+      <c r="N16" s="13" t="n">
+        <v>0.02520309601484017</v>
+      </c>
+      <c r="O16" s="13" t="n">
+        <v>0.003988632397666336</v>
+      </c>
+      <c r="P16" s="11" t="n">
+        <v>-19.17999999999988</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0-11.33 km</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0-5.665 km</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>0.003434128910463862</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>151.1313944391396</v>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>59.655</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5.665-11.33 km</t>
+        </is>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>0.00331826558464908</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>153.7042813295611</v>
+      </c>
+      <c r="L17" s="11" t="n">
+        <v>51.345</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>0.01702417224409047</v>
+      </c>
+      <c r="N17" s="13" t="n">
+        <v>-0.03373878175095402</v>
+      </c>
+      <c r="O17" s="13" t="n">
+        <v>-0.01759315206929202</v>
+      </c>
+      <c r="P17" s="11" t="n">
+        <v>-8.310000000000002</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0-9.07 km</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0-4.535 km</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>0.003316297623422761</v>
+      </c>
+      <c r="G18" s="11" t="n">
+        <v>156.7857634840562</v>
+      </c>
+      <c r="H18" s="11" t="n">
+        <v>22.745</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4.535-9.07 km</t>
+        </is>
+      </c>
+      <c r="J18" s="12" t="n">
+        <v>0.003265739209440973</v>
+      </c>
+      <c r="K18" s="11" t="n">
+        <v>161.1734923940778</v>
+      </c>
+      <c r="L18" s="11" t="n">
+        <v>17.255</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>0.02798550590639448</v>
+      </c>
+      <c r="N18" s="13" t="n">
+        <v>-0.01524543925873778</v>
+      </c>
+      <c r="O18" s="13" t="n">
+        <v>0.01216363937385667</v>
+      </c>
+      <c r="P18" s="11" t="n">
+        <v>-5.490000000000002</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0-5.6 km</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0-2.8 km</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>0.003731812169312169</v>
+      </c>
+      <c r="G19" s="11" t="n">
+        <v>139.9911386796633</v>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2.8-5.6 km</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>0.003708664021164021</v>
+      </c>
+      <c r="K19" s="11" t="n">
+        <v>148.0728934462773</v>
+      </c>
+      <c r="L19" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>0.05773047382025509</v>
+      </c>
+      <c r="N19" s="13" t="n">
+        <v>-0.006202924235711116</v>
+      </c>
+      <c r="O19" s="13" t="n">
+        <v>0.04867859481674941</v>
+      </c>
+      <c r="P19" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0-10.01 km</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0-5.005 km</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>0.003523293835793836</v>
+      </c>
+      <c r="G20" s="11" t="n">
+        <v>150.457746039768</v>
+      </c>
+      <c r="H20" s="11" t="n">
+        <v>35.095</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5.005-10.01 km</t>
+        </is>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>0.003527525715025715</v>
+      </c>
+      <c r="K20" s="11" t="n">
+        <v>150.5851424038704</v>
+      </c>
+      <c r="L20" s="11" t="n">
+        <v>48.905</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>0.0008467251933226283</v>
+      </c>
+      <c r="N20" s="13" t="n">
+        <v>0.001201114476711229</v>
+      </c>
+      <c r="O20" s="13" t="n">
+        <v>0.002044667453342863</v>
+      </c>
+      <c r="P20" s="11" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0-10.83 km</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0-5.415 km</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>0.003534527717930304</v>
+      </c>
+      <c r="G21" s="11" t="n">
+        <v>153.5099930456868</v>
+      </c>
+      <c r="H21" s="11" t="n">
+        <v>52.905</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5.415-10.83 km</t>
+        </is>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>0.003510374987175541</v>
+      </c>
+      <c r="K21" s="11" t="n">
+        <v>152.0560172922946</v>
+      </c>
+      <c r="L21" s="11" t="n">
+        <v>38.095</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>-0.009471538136018753</v>
+      </c>
+      <c r="N21" s="13" t="n">
+        <v>-0.0068333686088351</v>
+      </c>
+      <c r="O21" s="13" t="n">
+        <v>-0.01650828177081398</v>
+      </c>
+      <c r="P21" s="11" t="n">
+        <v>-14.81</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0-10.01 km</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0-5.005 km</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>0.003525467587967587</v>
+      </c>
+      <c r="G22" s="11" t="n">
+        <v>148.6363621455864</v>
+      </c>
+      <c r="H22" s="11" t="n">
+        <v>40.09999999999999</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5.005-10.01 km</t>
+        </is>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>0.003467539405039405</v>
+      </c>
+      <c r="K22" s="11" t="n">
+        <v>150.0452825155471</v>
+      </c>
+      <c r="L22" s="11" t="n">
+        <v>52.90000000000001</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>0.009478975061168127</v>
+      </c>
+      <c r="N22" s="13" t="n">
+        <v>-0.01643134746888353</v>
+      </c>
+      <c r="O22" s="13" t="n">
+        <v>-0.007159011890129241</v>
+      </c>
+      <c r="P22" s="11" t="n">
+        <v>12.80000000000001</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0-11.01 km</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0-5.505 km</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>0.003515333282874155</v>
+      </c>
+      <c r="G23" s="11" t="n">
+        <v>152.8283497956047</v>
+      </c>
+      <c r="H23" s="11" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5.505-11.01 km</t>
+        </is>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>0.003408086503851717</v>
+      </c>
+      <c r="K23" s="11" t="n">
+        <v>153.7458382043128</v>
+      </c>
+      <c r="L23" s="11" t="n">
+        <v>41.96</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>0.006003391451488982</v>
+      </c>
+      <c r="N23" s="13" t="n">
+        <v>-0.03050828197284106</v>
+      </c>
+      <c r="O23" s="13" t="n">
+        <v>-0.02531297142476641</v>
+      </c>
+      <c r="P23" s="11" t="n">
+        <v>-17.08</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0-10.14 km</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0-5.07 km</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>0.003499022938125502</v>
+      </c>
+      <c r="G24" s="11" t="n">
+        <v>154.0195466941556</v>
+      </c>
+      <c r="H24" s="11" t="n">
+        <v>59.56</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5.07-10.14 km</t>
+        </is>
+      </c>
+      <c r="J24" s="12" t="n">
+        <v>0.003342693038205859</v>
+      </c>
+      <c r="K24" s="11" t="n">
+        <v>154.766967615041</v>
+      </c>
+      <c r="L24" s="11" t="n">
+        <v>35.44000000000003</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>0.004852766658050678</v>
+      </c>
+      <c r="N24" s="13" t="n">
+        <v>-0.04467815806986175</v>
+      </c>
+      <c r="O24" s="13" t="n">
+        <v>-0.04171246304591802</v>
+      </c>
+      <c r="P24" s="11" t="n">
+        <v>-24.11999999999998</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0-9.74 km</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0-4.87 km</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>0.003443180089740665</v>
+      </c>
+      <c r="G25" s="11" t="n">
+        <v>135.326757685777</v>
+      </c>
+      <c r="H25" s="11" t="n">
+        <v>39.22</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4.87-9.74 km</t>
+        </is>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>0.003586822191801658</v>
+      </c>
+      <c r="K25" s="11" t="n">
+        <v>163.1626270523847</v>
+      </c>
+      <c r="L25" s="11" t="n">
+        <v>41.78</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>0.2056937581497471</v>
+      </c>
+      <c r="N25" s="13" t="n">
+        <v>0.04171785916426241</v>
+      </c>
+      <c r="O25" s="13" t="n">
+        <v>0.2038170415795761</v>
+      </c>
+      <c r="P25" s="11" t="n">
+        <v>2.560000000000002</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0-5.52 km</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0-2.76 km</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>0.003363358829844337</v>
+      </c>
+      <c r="G26" s="11" t="n">
+        <v>138.7008627998603</v>
+      </c>
+      <c r="H26" s="11" t="n">
+        <v>16.04</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2.76-5.52 km</t>
+        </is>
+      </c>
+      <c r="J26" s="12" t="n">
+        <v>0.003241411701556629</v>
+      </c>
+      <c r="K26" s="11" t="n">
+        <v>149.9797660939764</v>
+      </c>
+      <c r="L26" s="11" t="n">
+        <v>7.959999999999999</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>0.08131819129626527</v>
+      </c>
+      <c r="N26" s="13" t="n">
+        <v>-0.03625754326467512</v>
+      </c>
+      <c r="O26" s="13" t="n">
+        <v>0.04041047419285515</v>
+      </c>
+      <c r="P26" s="11" t="n">
+        <v>-8.08</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0-4.2 km</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0-2.1 km</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>0.003991402116402117</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>163.7334990334162</v>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>121.1</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2.1-4.2 km</t>
+        </is>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>0.003978174603174602</v>
+      </c>
+      <c r="K27" s="11" t="n">
+        <v>175.7664172901081</v>
+      </c>
+      <c r="L27" s="11" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>0.07349087589117076</v>
+      </c>
+      <c r="N27" s="13" t="n">
+        <v>-0.00331400165700102</v>
+      </c>
+      <c r="O27" s="13" t="n">
+        <v>0.06536232089680472</v>
+      </c>
+      <c r="P27" s="11" t="n">
+        <v>-38.2</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0-4.01 km</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0-2.005 km</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>0.002632048351343863</v>
+      </c>
+      <c r="G28" s="11" t="n">
+        <v>164.8077112872981</v>
+      </c>
+      <c r="H28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2.005-4.01 km</t>
+        </is>
+      </c>
+      <c r="J28" s="12" t="n">
+        <v>0.002442071903574398</v>
+      </c>
+      <c r="K28" s="11" t="n">
+        <v>184.401423016464</v>
+      </c>
+      <c r="L28" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>0.1188883188542649</v>
+      </c>
+      <c r="N28" s="13" t="n">
+        <v>-0.07217817547784311</v>
+      </c>
+      <c r="O28" s="13" t="n">
+        <v>0.03672857745343272</v>
+      </c>
+      <c r="P28" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0-5.45 km</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0-2.725 km</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>0.003270578491335372</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>166.646732248953</v>
+      </c>
+      <c r="H29" s="11" t="n">
+        <v>42.62500000000001</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2.725-5.45 km</t>
+        </is>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>0.003491229187903499</v>
+      </c>
+      <c r="K29" s="11" t="n">
+        <v>163.0643876030293</v>
+      </c>
+      <c r="L29" s="11" t="n">
+        <v>81.375</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>-0.02149663901343113</v>
+      </c>
+      <c r="N29" s="13" t="n">
+        <v>0.0674653420343494</v>
+      </c>
+      <c r="O29" s="13" t="n">
+        <v>0.04262100491028986</v>
+      </c>
+      <c r="P29" s="11" t="n">
+        <v>38.74999999999999</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0-11.02 km</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0-5.51 km</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>0.003541834711299321</v>
+      </c>
+      <c r="G30" s="11" t="n">
+        <v>153.8661321123987</v>
+      </c>
+      <c r="H30" s="11" t="n">
+        <v>50.22</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5.51-11.02 km</t>
+        </is>
+      </c>
+      <c r="J30" s="12" t="n">
+        <v>0.003570654365799556</v>
+      </c>
+      <c r="K30" s="11" t="n">
+        <v>157.3389337945478</v>
+      </c>
+      <c r="L30" s="11" t="n">
+        <v>42.78</v>
+      </c>
+      <c r="M30" s="13" t="n">
+        <v>0.02257027998606098</v>
+      </c>
+      <c r="N30" s="13" t="n">
+        <v>0.008136928131708965</v>
+      </c>
+      <c r="O30" s="13" t="n">
+        <v>0.02996520973911965</v>
+      </c>
+      <c r="P30" s="11" t="n">
+        <v>-7.439999999999998</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0-5.13 km</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0-2.565 km</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>0.004181805465309364</v>
+      </c>
+      <c r="G31" s="11" t="n">
+        <v>140.0469919234318</v>
+      </c>
+      <c r="H31" s="11" t="n">
+        <v>8.129999999999999</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2.565-5.13 km</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="n">
+        <v>0.003872667135946863</v>
+      </c>
+      <c r="K31" s="11" t="n">
+        <v>150.9134920681157</v>
+      </c>
+      <c r="L31" s="11" t="n">
+        <v>20.87</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <v>0.07759181397216341</v>
+      </c>
+      <c r="N31" s="13" t="n">
+        <v>-0.07392460790608091</v>
+      </c>
+      <c r="O31" s="13" t="n">
+        <v>-0.002073026908815612</v>
+      </c>
+      <c r="P31" s="11" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0-13.76 km</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>13.76</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0-6.88 km</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>0.003423436154177433</v>
+      </c>
+      <c r="G32" s="11" t="n">
+        <v>153.6918918918919</v>
+      </c>
+      <c r="H32" s="11" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>6.88-13.76 km</t>
+        </is>
+      </c>
+      <c r="J32" s="12" t="n">
+        <v>0.003388108311800172</v>
+      </c>
+      <c r="K32" s="11" t="n">
+        <v>154.4443892750745</v>
+      </c>
+      <c r="L32" s="11" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="M32" s="13" t="n">
+        <v>0.004896142365869993</v>
+      </c>
+      <c r="N32" s="13" t="n">
+        <v>-0.0103194103194103</v>
+      </c>
+      <c r="O32" s="13" t="n">
+        <v>-0.005503920578940447</v>
+      </c>
+      <c r="P32" s="11" t="n">
+        <v>-38.40000000000001</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0-7.44 km</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0-3.72 km</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>0.00334839207487057</v>
+      </c>
+      <c r="G33" s="11" t="n">
+        <v>165.947407545066</v>
+      </c>
+      <c r="H33" s="11" t="n">
+        <v>34.24</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3.72-7.44 km</t>
+        </is>
+      </c>
+      <c r="J33" s="12" t="n">
+        <v>0.003278698725607328</v>
+      </c>
+      <c r="K33" s="11" t="n">
+        <v>167.6394002657051</v>
+      </c>
+      <c r="L33" s="11" t="n">
+        <v>38.76</v>
+      </c>
+      <c r="M33" s="13" t="n">
+        <v>0.01019595753660441</v>
+      </c>
+      <c r="N33" s="13" t="n">
+        <v>-0.02081397509756544</v>
+      </c>
+      <c r="O33" s="13" t="n">
+        <v>-0.01094881420866467</v>
+      </c>
+      <c r="P33" s="11" t="n">
+        <v>4.519999999999996</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0-9.08 km</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0-4.54 km</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>0.00318322728014358</v>
+      </c>
+      <c r="G34" s="11" t="n">
+        <v>153.5453933880061</v>
+      </c>
+      <c r="H34" s="11" t="n">
+        <v>38.16</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>4.54-9.08 km</t>
+        </is>
+      </c>
+      <c r="J34" s="12" t="n">
+        <v>0.003077989884157285</v>
+      </c>
+      <c r="K34" s="11" t="n">
+        <v>159.1588921282799</v>
+      </c>
+      <c r="L34" s="11" t="n">
+        <v>38.84000000000001</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>0.03655921298849085</v>
+      </c>
+      <c r="N34" s="13" t="n">
+        <v>-0.03305996924654031</v>
+      </c>
+      <c r="O34" s="13" t="n">
+        <v>0.002285362439873873</v>
+      </c>
+      <c r="P34" s="11" t="n">
+        <v>0.6800000000000139</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0-6.01 km</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0-3.005 km</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>0.00396228122881617</v>
+      </c>
+      <c r="G35" s="11" t="n">
+        <v>131.927094927265</v>
+      </c>
+      <c r="H35" s="11" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3.005-6.01 km</t>
+        </is>
+      </c>
+      <c r="J35" s="12" t="n">
+        <v>0.003817961576385037</v>
+      </c>
+      <c r="K35" s="11" t="n">
+        <v>138.6662295148119</v>
+      </c>
+      <c r="L35" s="11" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>0.05108226320955778</v>
+      </c>
+      <c r="N35" s="13" t="n">
+        <v>-0.03642337433838638</v>
+      </c>
+      <c r="O35" s="13" t="n">
+        <v>0.01263657380765693</v>
+      </c>
+      <c r="P35" s="11" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0-13.01 km</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0-6.505 km</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>0.003324454835311868</v>
+      </c>
+      <c r="G36" s="11" t="n">
+        <v>153.4928684203484</v>
+      </c>
+      <c r="H36" s="11" t="n">
+        <v>70.06999999999999</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>6.505-13.01 km</t>
+        </is>
+      </c>
+      <c r="J36" s="12" t="n">
+        <v>0.003241007629458822</v>
+      </c>
+      <c r="K36" s="11" t="n">
+        <v>153.8070599214954</v>
+      </c>
+      <c r="L36" s="11" t="n">
+        <v>34.93</v>
+      </c>
+      <c r="M36" s="13" t="n">
+        <v>0.002046945271011458</v>
+      </c>
+      <c r="N36" s="13" t="n">
+        <v>-0.02510101956166866</v>
+      </c>
+      <c r="O36" s="13" t="n">
+        <v>-0.02365194361582224</v>
+      </c>
+      <c r="P36" s="11" t="n">
+        <v>-35.13999999999999</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0-7.02 km</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0-3.51 km</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>0.003746504695578769</v>
+      </c>
+      <c r="G37" s="11" t="n">
+        <v>134.6482599588093</v>
+      </c>
+      <c r="H37" s="11" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3.51-7.02 km</t>
+        </is>
+      </c>
+      <c r="J37" s="12" t="n">
+        <v>0.003623311702015406</v>
+      </c>
+      <c r="K37" s="11" t="n">
+        <v>140.9769935021205</v>
+      </c>
+      <c r="L37" s="11" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="M37" s="13" t="n">
+        <v>0.04700197050631871</v>
+      </c>
+      <c r="N37" s="13" t="n">
+        <v>-0.03288211374958161</v>
+      </c>
+      <c r="O37" s="13" t="n">
+        <v>0.01241818226184599</v>
+      </c>
+      <c r="P37" s="11" t="n">
+        <v>-2.019999999999996</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>4x15 seonds strides if recovered</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>park_run</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0-4 km</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0-2 km</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>0.003240740740740741</v>
+      </c>
+      <c r="G38" s="11" t="n">
+        <v>149.9785714285714</v>
+      </c>
+      <c r="H38" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2-4 km</t>
+        </is>
+      </c>
+      <c r="J38" s="12" t="n">
+        <v>0.003229166666666667</v>
+      </c>
+      <c r="K38" s="11" t="n">
+        <v>152.4928315412186</v>
+      </c>
+      <c r="L38" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M38" s="13" t="n">
+        <v>0.01676412895988033</v>
+      </c>
+      <c r="N38" s="13" t="n">
+        <v>-0.003571428571428559</v>
+      </c>
+      <c r="O38" s="13" t="n">
+        <v>0.01296259298868274</v>
+      </c>
+      <c r="P38" s="11" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Training plan: 0-4</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Easy, 145-155 bpm</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>easy_run</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0-6.01 km</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0-3.005 km</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>0.00355302890244654</v>
+      </c>
+      <c r="G39" s="11" t="n">
+        <v>138.2996270921863</v>
+      </c>
+      <c r="H39" s="11" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3.005-6.01 km</t>
+        </is>
+      </c>
+      <c r="J39" s="12" t="n">
+        <v>0.003495408886423862</v>
+      </c>
+      <c r="K39" s="11" t="n">
+        <v>143.674365303244</v>
+      </c>
+      <c r="L39" s="11" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="M39" s="13" t="n">
+        <v>0.03886299857826159</v>
+      </c>
+      <c r="N39" s="13" t="n">
+        <v>-0.016217153759431</v>
+      </c>
+      <c r="O39" s="13" t="n">
+        <v>0.02154135186110073</v>
+      </c>
+      <c r="P39" s="11" t="n">
+        <v>-3.019999999999998</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>RPE 2-3/10. Slow enough to protect volleyball practice</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:S39"/>
+  <conditionalFormatting sqref="O2:O39">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.05"/>
+        <cfvo type="num" val="0.1"/>
+        <color rgb="00C6EFCE"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00FFC7CE"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Session Name</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Analysis Segment</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Segment Distance (km)</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>First Half Range</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>First Half Pace</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>First Half Avg HR</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>First Half Ascent</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>Second Half Range</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>Second Half Pace</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>Second Half Avg HR</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>Second Half Ascent</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>HR Drift %</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>Pace Change %</t>
+        </is>
+      </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>Aerobic Decoupling %</t>
+        </is>
+      </c>
+      <c r="P1" s="9" t="inlineStr">
+        <is>
+          <t>Ascent Difference</t>
+        </is>
+      </c>
+      <c r="Q1" s="9" t="inlineStr">
+        <is>
+          <t>Analysis Source</t>
+        </is>
+      </c>
+      <c r="R1" s="9" t="inlineStr">
+        <is>
+          <t>Context Flag</t>
+        </is>
+      </c>
+      <c r="S1" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>long_run</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0-20.01 km</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0-10.005 km</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="n">
+        <v>0.003460705989597794</v>
+      </c>
+      <c r="G2" s="11" t="n">
+        <v>157.905976677603</v>
+      </c>
+      <c r="H2" s="11" t="n">
+        <v>77.10000000000002</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10.005-20.01 km</t>
+        </is>
+      </c>
+      <c r="J2" s="12" t="n">
+        <v>0.003358800923612268</v>
+      </c>
+      <c r="K2" s="11" t="n">
+        <v>164.2870872804986</v>
+      </c>
+      <c r="L2" s="11" t="n">
+        <v>86.89999999999998</v>
+      </c>
+      <c r="M2" s="13" t="n">
+        <v>0.04041082381526229</v>
+      </c>
+      <c r="N2" s="13" t="n">
+        <v>-0.02944632288666893</v>
+      </c>
+      <c r="O2" s="13" t="n">
+        <v>0.009679933758513393</v>
+      </c>
+      <c r="P2" s="11" t="n">
+        <v>9.799999999999955</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>long_run</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0-26.01 km</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>26.01</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0-13.005 km</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="n">
+        <v>0.003398354621441896</v>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>153.7138928898782</v>
+      </c>
+      <c r="H3" s="11" t="n">
+        <v>116.065</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>13.005-26.01 km</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="n">
+        <v>0.003263079015193587</v>
+      </c>
+      <c r="K3" s="11" t="n">
+        <v>159.6196645302059</v>
+      </c>
+      <c r="L3" s="11" t="n">
+        <v>111.935</v>
+      </c>
+      <c r="M3" s="13" t="n">
+        <v>0.03842054565984276</v>
+      </c>
+      <c r="N3" s="13" t="n">
+        <v>-0.03980620662563827</v>
+      </c>
+      <c r="O3" s="13" t="n">
+        <v>-0.002923559429333089</v>
+      </c>
+      <c r="P3" s="11" t="n">
+        <v>-4.130000000000024</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>long_run</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0-24.47 km</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>24.47</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0-12.235 km</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>0.003385688636122841</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>145.3504096786136</v>
+      </c>
+      <c r="H4" s="11" t="n">
+        <v>96.99499999999999</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12.235-24.47 km</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="n">
+        <v>0.003428210469357793</v>
+      </c>
+      <c r="K4" s="11" t="n">
+        <v>148.2323277616429</v>
+      </c>
+      <c r="L4" s="11" t="n">
+        <v>98.00500000000001</v>
+      </c>
+      <c r="M4" s="13" t="n">
+        <v>0.01982738190694877</v>
+      </c>
+      <c r="N4" s="13" t="n">
+        <v>0.01255928639783188</v>
+      </c>
+      <c r="O4" s="13" t="n">
+        <v>0.03160425938482669</v>
+      </c>
+      <c r="P4" s="11" t="n">
+        <v>1.010000000000019</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>long_run</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0-31.21 km</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>31.21</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0-15.605 km</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>0.003452626769672588</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>143.8260652878146</v>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>118.63</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15.605-31.21 km</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>0.003436190916966309</v>
+      </c>
+      <c r="K5" s="11" t="n">
+        <v>148.178936826019</v>
+      </c>
+      <c r="L5" s="11" t="n">
+        <v>112.37</v>
+      </c>
+      <c r="M5" s="13" t="n">
+        <v>0.03026483085311238</v>
+      </c>
+      <c r="N5" s="13" t="n">
+        <v>-0.004760390798869252</v>
+      </c>
+      <c r="O5" s="13" t="n">
+        <v>0.024733126452401</v>
+      </c>
+      <c r="P5" s="11" t="n">
+        <v>-6.259999999999977</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>long_run</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0-22.33 km</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0-11.165 km</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>0.003416746487867177</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>146.8610658118893</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>133.33</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>11.165-22.33 km</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="n">
+        <v>0.003501781982385431</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>141.671700688126</v>
+      </c>
+      <c r="L6" s="11" t="n">
+        <v>103.67</v>
+      </c>
+      <c r="M6" s="13" t="n">
+        <v>-0.03533519993931022</v>
+      </c>
+      <c r="N6" s="13" t="n">
+        <v>0.02488785598235421</v>
+      </c>
+      <c r="O6" s="13" t="n">
+        <v>-0.01145652666731745</v>
+      </c>
+      <c r="P6" s="11" t="n">
+        <v>-29.65999999999998</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>long_run</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0-20.58 km</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0-10.29 km</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>0.003984068495122918</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>136.1262429207862</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>55.45</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10.29-20.58 km</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>0.003807341719756686</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>143.0278468746861</v>
+      </c>
+      <c r="L7" s="11" t="n">
+        <v>62.55</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>0.05070002525461681</v>
+      </c>
+      <c r="N7" s="13" t="n">
+        <v>-0.04435836772951351</v>
+      </c>
+      <c r="O7" s="13" t="n">
+        <v>0.004076005346214995</v>
+      </c>
+      <c r="P7" s="11" t="n">
+        <v>7.100000000000001</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Automatic full session</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>long_run</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0-12 km</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0-6 km</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>0.003219521604938272</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>152.1899340922708</v>
+      </c>
+      <c r="H8" s="11" t="n">
+        <v>66</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6-12 km</t>
+        </is>
+      </c>
+      <c r="J8" s="12" t="n">
+        <v>0.003190586419753086</v>
+      </c>
+      <c r="K8" s="11" t="n">
+        <v>153.1813784764208</v>
+      </c>
+      <c r="L8" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>0.006514520096637222</v>
+      </c>
+      <c r="N8" s="13" t="n">
+        <v>-0.0089874176153385</v>
+      </c>
+      <c r="O8" s="13" t="n">
+        <v>-0.00253787071462952</v>
+      </c>
+      <c r="P8" s="11" t="n">
+        <v>-35</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Training plan: 0-12</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>First 12 km easy, not above 155-158. Last 3 km sits close to LT! (163 bpm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>long_run</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0-12 km</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0-6 km</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>0.003323688271604939</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>151.2060359837493</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>67</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6-12 km</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>0.003327546296296296</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>151.0220289855072</v>
+      </c>
+      <c r="L9" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>-0.001216928921156435</v>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>0.001160766105629651</v>
+      </c>
+      <c r="O9" s="13" t="n">
+        <v>-5.757870048705982e-05</v>
+      </c>
+      <c r="P9" s="11" t="n">
+        <v>-32</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Training plan: 0-12</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Review conditions, terrain and HR reliability</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 km easy, then 4 km controlled steady (155-160), then 1 km easy. </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:S9"/>
+  <conditionalFormatting sqref="O2:O9">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.05"/>
+        <cfvo type="num" val="0.1"/>
+        <color rgb="00C6EFCE"/>
+        <color rgb="00FFEB9C"/>
+        <color rgb="00FFC7CE"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Session Name</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Block Name</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Start Distance</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>End Distance</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Block Distance</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>Block Time</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>Average Pace</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>Average HR</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>Maximum HR</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>Ascent</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>Efficiency</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>park_run</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Fast Finish</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="12" t="n">
+        <v>0.002743055555555555</v>
+      </c>
+      <c r="H2" s="12" t="n">
+        <v>0.002743055555555555</v>
+      </c>
+      <c r="I2" s="14" t="n">
+        <v>165</v>
+      </c>
+      <c r="J2" s="14" t="n">
+        <v>185</v>
+      </c>
+      <c r="K2" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L2" s="14" t="n">
+        <v>0.09205983889528194</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Easy, 145-155 bpm</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>long_run</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Controlled</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F3" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>0.009085648148148148</v>
+      </c>
+      <c r="H3" s="12" t="n">
+        <v>0.00302854938271605</v>
+      </c>
+      <c r="I3" s="14" t="n">
+        <v>159.6165605095541</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>166</v>
+      </c>
+      <c r="K3" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="L3" s="14" t="n">
+        <v>0.08619382437210193</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>First 12 km easy, not above 155-158. Last 3 km sits close to LT! (163 bpm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>long_run</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Controlled</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="H4" s="12" t="n">
+        <v>0.003125</v>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>159.1898148148148</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>166</v>
+      </c>
+      <c r="K4" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="L4" s="14" t="n">
+        <v>0.08375745237749019</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 km easy, then 4 km controlled steady (155-160), then 1 km easy. </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>long_run</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>0.7399999999999984</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>0.002569444444444439</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>0.003472222222222222</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>152</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>161</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>0.9999999999999979</v>
+      </c>
+      <c r="L5" s="14" t="n">
+        <v>0.07894736842105264</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 km easy, then 4 km controlled steady (155-160), then 1 km easy. </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12360,10 +16251,10 @@
         <v>144.8</v>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I37" t="n">
         <v>217</v>
@@ -12406,8 +16297,11 @@
       <c r="F38" t="n">
         <v>154</v>
       </c>
+      <c r="G38" t="n">
+        <v>5</v>
+      </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
         <v>30</v>
@@ -15489,10 +19383,10 @@
         <v>136</v>
       </c>
       <c r="H74" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I74" t="n">
         <v>2</v>
-      </c>
-      <c r="I74" t="n">
-        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>30</v>
@@ -15531,8 +19425,11 @@
       <c r="G75" t="n">
         <v>153</v>
       </c>
+      <c r="H75" t="n">
+        <v>3.5</v>
+      </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>142</v>
@@ -15614,8 +19511,11 @@
       <c r="G77" t="n">
         <v>154</v>
       </c>
+      <c r="H77" t="n">
+        <v>5</v>
+      </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>30</v>
@@ -16839,10 +20739,10 @@
         <v>136</v>
       </c>
       <c r="G28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H28" t="n">
         <v>2</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>30</v>
@@ -18071,8 +21971,11 @@
       <c r="F28" t="n">
         <v>141</v>
       </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>30</v>
@@ -18489,8 +22392,11 @@
       <c r="F9" t="n">
         <v>153</v>
       </c>
+      <c r="G9" t="n">
+        <v>3.5</v>
+      </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>142</v>
